--- a/xlsx/nodes.xlsx
+++ b/xlsx/nodes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3f29f64542198b99/ドキュメント/Otanilab/lab-competition-2026/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3f29f64542198b99/ドキュメント/Otanilab/lab-competition-2026/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{1B817FDC-7841-4ADA-A286-0455F009FB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BECC543-5DD3-49A6-A3A2-DCE1671BBB96}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{1B817FDC-7841-4ADA-A286-0455F009FB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5118860-9AF2-4890-8FC5-26D9E8800325}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{AF99DB99-C861-47A3-BECA-EEFDB403CDB6}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{AF99DB99-C861-47A3-BECA-EEFDB403CDB6}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
